--- a/2026.02.16_Файлы загрузки и выгрузки данных/Загрузочные файлы/Загрузочные данные_MoSCoW_коллектив.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Загрузочные файлы/Загрузочные данные_MoSCoW_коллектив.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\79147\Documents\Документы, инвестиции, личные финансы\2024.07.03_Альфа-банк\Магистратура ВШЭ\20_Магистерская диссертация\2026.02.11_Файлы загрузки и выгрузки\20260218_обновленные файлы\2026.04.04_Обновление\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\79147\Documents\Документы, инвестиции, личные финансы\2024.07.03_Альфа-банк\Магистратура ВШЭ\20_Магистерская диссертация\2026.02.11_Файлы загрузки и выгрузки\2026.04.08_Обновление\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77CC4A8A-835B-4547-8379-5A6A0CAFF50E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF2F18E0-3BE4-46A7-9C52-5040E7E02CD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="815" activeTab="2" xr2:uid="{DFAEC376-1DD0-4C05-9E4E-4B59B56AAC43}"/>
   </bookViews>
@@ -174,9 +174,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -188,6 +185,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -475,7 +475,7 @@
   <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39" customWidth="1"/>
+    <col min="1" max="1" width="31" customWidth="1"/>
     <col min="2" max="2" width="11.42578125" customWidth="1"/>
     <col min="3" max="3" width="12.140625" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" customWidth="1"/>
@@ -487,7 +487,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -501,16 +501,16 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="7" t="s">
+      <c r="B4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>6</v>
       </c>
     </row>
@@ -537,142 +537,142 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="B9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="B10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="4" t="s">
+      <c r="B11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="B12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="4" t="s">
+      <c r="B13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="4" t="s">
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="4" t="s">
+      <c r="B15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="4" t="s">
+      <c r="B16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="4" t="s">
+      <c r="B17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="4" t="s">
+      <c r="B18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>6</v>
       </c>
     </row>
@@ -691,7 +691,7 @@
   <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39" customWidth="1"/>
+    <col min="1" max="1" width="30.5703125" customWidth="1"/>
     <col min="2" max="2" width="11.42578125" customWidth="1"/>
     <col min="3" max="3" width="12.140625" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" customWidth="1"/>
@@ -703,7 +703,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -717,16 +717,16 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="7" t="s">
+      <c r="B4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>6</v>
       </c>
     </row>
@@ -753,142 +753,142 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="B9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="B10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="4" t="s">
+      <c r="B11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="B12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="4" t="s">
+      <c r="B13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="4" t="s">
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="4" t="s">
+      <c r="B15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" s="4" t="s">
+      <c r="B16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="4" t="s">
+      <c r="B17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" s="4" t="s">
+      <c r="B18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>6</v>
       </c>
     </row>
@@ -907,7 +907,7 @@
   <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39" customWidth="1"/>
+    <col min="1" max="1" width="30.28515625" customWidth="1"/>
     <col min="2" max="2" width="11.42578125" customWidth="1"/>
     <col min="3" max="3" width="12.140625" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" customWidth="1"/>
@@ -919,7 +919,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -933,16 +933,16 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="7" t="s">
+      <c r="B4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>6</v>
       </c>
     </row>
@@ -969,142 +969,142 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="B9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="4" t="s">
+      <c r="B11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="B12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="4" t="s">
+      <c r="B13" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="4" t="s">
+      <c r="B14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="4" t="s">
+      <c r="B15" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="4" t="s">
+      <c r="B16" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="4" t="s">
+      <c r="B17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="4" t="s">
+      <c r="B18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>6</v>
       </c>
     </row>
